--- a/report/issue.xlsx
+++ b/report/issue.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\대시보드_리뉴얼\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A38DE96-F34D-4A48-9279-13E71CF59A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C7245A-87EB-467A-933A-5FC5A6B2520A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="0" windowWidth="28800" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="26.05월" sheetId="1" r:id="rId1"/>
+    <sheet name="26.04월" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>

--- a/report/issue.xlsx
+++ b/report/issue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\대시보드_리뉴얼\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C7245A-87EB-467A-933A-5FC5A6B2520A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45DFD814-B04E-415D-965B-0A6E81F06799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="0" windowWidth="28800" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="26.04월" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="60">
   <si>
     <t>구분</t>
   </si>
@@ -204,6 +204,17 @@
   </si>
   <si>
     <t>낮잠이불 Issue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[엄마감동] 배터리 분리형 휴대용 분유포트 뚜껑세트 및 실리콘 2종 무상자재 공급 요청 건</t>
+  </si>
+  <si>
+    <t>[꿈비] 배터리 분리형 휴대용 분유포트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뚜껑 무상자재 지급 요청</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -664,20 +675,20 @@
         <v>37</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="O2" s="5">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2" t="s">
         <v>53</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -713,17 +724,17 @@
         <v>38</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="O3" s="5">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2" t="s">
         <v>53</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -756,20 +767,20 @@
         <v>37</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="O4" s="5">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2" t="s">
         <v>53</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -799,25 +810,23 @@
         <v>54</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="O5" s="5">
-        <v>46111</v>
-      </c>
-      <c r="P5" s="5">
-        <v>46149</v>
-      </c>
+        <v>46153</v>
+      </c>
+      <c r="P5" s="2"/>
       <c r="Q5" s="2" t="s">
         <v>53</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -850,22 +859,22 @@
         <v>46</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="O6" s="5">
-        <v>46049</v>
+        <v>46111</v>
       </c>
       <c r="P6" s="5">
-        <v>46050</v>
+        <v>46149</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>53</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -886,6 +895,33 @@
         <v>1</v>
       </c>
       <c r="G7" s="2"/>
+      <c r="J7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="O7" s="5">
+        <v>46049</v>
+      </c>
+      <c r="P7" s="5">
+        <v>46050</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">

--- a/report/issue.xlsx
+++ b/report/issue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\대시보드_리뉴얼\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45DFD814-B04E-415D-965B-0A6E81F06799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3966C6-E188-422C-93F5-E920601BB3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28800" yWindow="0" windowWidth="28800" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="26.04월" sheetId="1" r:id="rId1"/>
@@ -222,8 +222,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="6" formatCode="&quot;₩&quot;#,##0;[Red]\-&quot;₩&quot;#,##0"/>
+    <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -276,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -291,6 +292,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -683,7 +687,9 @@
       <c r="O2" s="5">
         <v>46162</v>
       </c>
-      <c r="P2" s="2"/>
+      <c r="P2" s="6">
+        <v>46163</v>
+      </c>
       <c r="Q2" s="2" t="s">
         <v>53</v>
       </c>

--- a/report/issue.xlsx
+++ b/report/issue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\대시보드_리뉴얼\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3966C6-E188-422C-93F5-E920601BB3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75637544-EB9C-4A0E-9A7E-2A024F5176B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="0" windowWidth="28800" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27555" yWindow="3030" windowWidth="20355" windowHeight="9810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="26.04월" sheetId="1" r:id="rId1"/>
@@ -676,7 +676,7 @@
         <v>54</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>58</v>

--- a/report/issue.xlsx
+++ b/report/issue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\대시보드_리뉴얼\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75637544-EB9C-4A0E-9A7E-2A024F5176B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A27F592-A85F-4A19-BFF4-C5F4FDB53642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27555" yWindow="3030" windowWidth="20355" windowHeight="9810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27900" yWindow="3375" windowWidth="20355" windowHeight="9810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="26.04월" sheetId="1" r:id="rId1"/>
@@ -214,7 +214,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>뚜껑 무상자재 지급 요청</t>
+    <t>뚜껑세트 및 실리콘 2종  무상자재 지급 요청</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
